--- a/jpcore-r4b/develop/StructureDefinition-jp-condition.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-condition.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-condition.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -380,7 +380,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -611,7 +611,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-category|4.3.0</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -641,7 +641,7 @@
 このプロファイルではHL70421 Severity of Illness Code（MI 軽度, MO 中度, SE 重度）を採用。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConditionSeverity_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConditionSeverity_VS|2.0.0-dev-temp</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -681,7 +681,7 @@
     <t>Identification of the condition or diagnosis.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.3.0</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -726,7 +726,7 @@
     <t>SNOMED CT Body site concepts</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.3.0</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -995,7 +995,7 @@
     <t>Codes describing condition stages (e.g. Cancer stages).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage|4.3.0</t>
   </si>
   <si>
     <t xml:space="preserve">con-1
@@ -1033,7 +1033,7 @@
     <t>Codes describing the kind of condition staging (e.g. clinical or pathological).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage-type</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage-type|4.3.0</t>
   </si>
   <si>
     <t>./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="stage type"]</t>
@@ -1080,7 +1080,7 @@
     <t>Codes that describe the manifestation or symptoms of a condition.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom</t>
+    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom|4.3.0</t>
   </si>
   <si>
     <t xml:space="preserve">con-2
@@ -1099,7 +1099,7 @@
     <t>Condition.evidence.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.3.0)
 </t>
   </si>
   <si>
@@ -1436,17 +1436,17 @@
   <dimension ref="A1:AP38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="35.88671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="30.765625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="30.765625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="185.2109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="158.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1455,28 +1455,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="85.23828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.6171875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="73.078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.63671875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="68.20703125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="222.1015625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="58.4765625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="190.4140625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4b/develop/StructureDefinition-jp-condition.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -641,7 +641,7 @@
 このプロファイルではHL70421 Severity of Illness Code（MI 軽度, MO 中度, SE 重度）を採用。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConditionSeverity_VS|2.0.0-dev-temp</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConditionSeverity_VS|2.0.0-dev</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -1461,7 +1461,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="73.078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.63671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="53.95703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4b/develop/StructureDefinition-jp-condition.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-condition.xlsx
@@ -275,8 +275,8 @@
 健康上の懸念となるレベルに達した、身体的、精神的、社会的な負の状態(condition)や問題（problem／issue）、医療者による診断(diagnosis)、生じたイベント(event)、置かれている状況(situation)、臨床的概念(clinical concept)。</t>
   </si>
   <si>
-    <t>con-3:Condition.clinicalStatus SHOULD be present if verificationStatus is not entered-in-error and category is problem-list-item {verificationStatus.empty().not() and verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').exists().not() and category.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-category' and code='problem-list-item').exists() implies clinicalStatus.empty().not()}
-con-4:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:Condition.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>con-3:verificationStatus」が「entered-in-error」でなく、「category」が「problem-list-item」である場合、「condition.clinicalStatus」が存在している必要があります。 / Condition.clinicalStatus SHOULD be present if verificationStatus is not entered-in-error and category is problem-list-item {verificationStatus.empty().not() and verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').exists().not() and category.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-category' and code='problem-list-item').exists() implies clinicalStatus.empty().not()}
+con-4:もし状態が軽減された場合、臨床状態は不活動、解決、または寛解でなければなりません。 / If condition is abated, then clinicalStatus must be either inactive, resolved, or remission {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:verificationStatusがentered-in-errorである場合、condition.clinicalStatusは存在してはなりません。 / Condition.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -307,13 +307,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -326,16 +326,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -346,13 +346,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -365,19 +365,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>人間の言語。 / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -400,10 +400,10 @@
     <t>Text summary of the resource, for human interpretation. このリソースを人間が解釈するためのテキスト要約</t>
   </si>
   <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -423,19 +423,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>含まれている、インラインのリソース / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -453,33 +453,33 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装によって定義される追加コンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Condition.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張により、安全に無視できない拡張を、安全に無視できる大多数の拡張と明確に区別することができます。これにより、実装者が拡張の存在を禁止する必要がなくなり、相互運用性が促進されます。詳細については、[修飾子拡張の定義](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension)を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -492,16 +492,16 @@
 </t>
   </si>
   <si>
-    <t>External Ids for this condition</t>
-  </si>
-  <si>
-    <t>Business identifiers assigned to this condition by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
-  </si>
-  <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4B/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
-  </si>
-  <si>
-    <t>Allows identification of the condition as it is known by various participating systems and in a way that remains consistent across servers.</t>
+    <t>この状態の外部ID。 / External Ids for this condition</t>
+  </si>
+  <si>
+    <t>サーバーからサーバーへ伝搬するにつれて更新され、パフォーマーまたは他のシステムによって割り当てられたビジネスidentifierが、この状態に対して一定の値を保持します。 / Business identifiers assigned to this condition by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
+  </si>
+  <si>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません（[discussion]（resource.html＃identifiers）を参照）。 identifierが単一のリソースインスタンスにのみ表示されることが最善の方法ですが、ビジネス上の実践によっては、同じidentifierを持つ複数のリソースインスタンスが存在する場合があります。 たとえば、複数の患者と個人リソースインスタンスが同じ社会保険番号を共有する場合があります。 / This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4B/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+  </si>
+  <si>
+    <t>様々な参加システムによって知られている状態の識別を可能にし、サーバー間で一貫性を保つ方法で識別できるようにする。 / Allows identification of the condition as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
     <t>Event.identifier</t>
@@ -527,13 +527,13 @@
 この患者状態の臨床的ステータス（アクティブか否かなど）</t>
   </si>
   <si>
-    <t>The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
+    <t>データ型はCodeableConceptです。なぜなら、clinicalStatusには一定の臨床判断が含まれるため、必要なFHIR値セットが許容するよりもさらに特定性が必要になる場合があるためです。例えば、SNOMEDコーディングは追加の特定性を許容する場合があります。 / The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>The clinical status of the condition or diagnosis.</t>
+    <t>病態や診断の臨床状態。 / The clinical status of the condition or diagnosis.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-clinical|4.3.0</t>
@@ -569,11 +569,12 @@
  この患者状態が存在するかどうかの検証状況。</t>
   </si>
   <si>
-    <t>verificationStatus is not required.  For example, when a patient has abdominal pain in the ED, there is not likely going to be a verification status.
+    <t>検証状態は必須ではありません。例えば、救急治療室で患者が腹痛を訴えた場合、一般的には検証状態が必要ないでしょう。
+データ型はCodeableConceptであり、検証状態には臨床的な判断が必要なため、必要なFHIR値のセットよりも詳細な仕様が必要になる場合があります。例えば、SNOMEDのコーディングではさらに詳細な情報を含むことができます。 / verificationStatus is not required.  For example, when a patient has abdominal pain in the ED, there is not likely going to be a verification status.
 The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>The verification status to support or decline the clinical status of the condition or diagnosis.</t>
+    <t>状態や診断の臨床状況を支持または拒否するための検証状況 / The verification status to support or decline the clinical status of the condition or diagnosis.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-ver-status|4.3.0</t>
@@ -602,10 +603,10 @@
     <t>problem-list-item | encounter-diagnosis（プロブレムリスト | 一時的な診断）</t>
   </si>
   <si>
-    <t>A category assigned to the condition.</t>
-  </si>
-  <si>
-    <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
+    <t>状態に割り当てられたカテゴリー。 / A category assigned to the condition.</t>
+  </si>
+  <si>
+    <t>分類はしばしば文脈に強く依存しており、他の文脈では区別が不十分であるか、あまり役に立たないように見えることがあります。 / The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
   </si>
   <si>
     <t>extensible</t>
@@ -669,16 +670,16 @@
     <t>Identification of the condition, problem or diagnosis. この患者状態の識別コード</t>
   </si>
   <si>
-    <t>Identification of the condition, problem or diagnosis.</t>
-  </si>
-  <si>
-    <t>0..1 to account for primarily narrative only resources.</t>
+    <t>状態、問題、診断の特定。 / Identification of the condition, problem or diagnosis.</t>
+  </si>
+  <si>
+    <t>主にナラティブのみのリソースを考慮して0..1としている。 / 0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>Identification of the condition or diagnosis.</t>
+    <t>状態や診断の特定 / Identification of the condition or diagnosis.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-code|4.3.0</t>
@@ -717,13 +718,13 @@
     <t>Anatomical location, if relevant. もし関連するのであれば、その人体部位</t>
   </si>
   <si>
-    <t>The anatomical location where this condition manifests itself.</t>
-  </si>
-  <si>
-    <t>Only used if not implicit in code found in Condition.code. If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).  May be a summary code, or a reference to a very precise definition of the location, or both.</t>
-  </si>
-  <si>
-    <t>SNOMED CT Body site concepts</t>
+    <t>この症状が現れる解剖学的位置。 / The anatomical location where this condition manifests itself.</t>
+  </si>
+  <si>
+    <t>Condition.code」で暗黙的に表現されない場合にのみ使用します。ユースケースがBodySiteリソースから属性を必要とする場合（例えば、別々に識別して追跡するために）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用してください。概要コードであることも、位置の非常に正確な定義への参照であることもあります。 / Only used if not implicit in code found in Condition.code. If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).  May be a summary code, or a reference to a very precise definition of the location, or both.</t>
+  </si>
+  <si>
+    <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。 / SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site|4.3.0</t>
@@ -752,10 +753,10 @@
     <t>Who has the condition? 誰がこの状態を有するか</t>
   </si>
   <si>
-    <t>Indicates the patient or group who the condition record is associated with.</t>
-  </si>
-  <si>
-    <t>Group is typically used for veterinary or public health use cases.</t>
+    <t>その病状記録が関連する患者またはグループを示します。 / Indicates the patient or group who the condition record is associated with.</t>
+  </si>
+  <si>
+    <t>Groupは通常、獣医学または公衆衛生のユースケースに使用される。 / Group is typically used for veterinary or public health use cases.</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -784,7 +785,7 @@
 この患者状態の記録やレコード作成に関連する受療の状況（外来、入院、救急、在宅など）</t>
   </si>
   <si>
-    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. This record indicates the encounter this particular record is associated with.  In the case of a "new" diagnosis reflecting ongoing/revised information about the condition, this might be distinct from the first encounter in which the underlying condition was first "known".</t>
+    <t>通常、イベントが発生した受療行動の中で行われることが多いですが、公式的に受療行動が完了する前または後に開始される場合がありますが、それでも受療行動の文脈に関連する活動があります。この記録は、この特定の記録が関連付けられた出来事を示します。 「新しい」診断が、継続的に修正された情報を反映する場合、これは最初に患者が変化に気づいた最初の受療行動とは異なる場合があります。 / This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. This record indicates the encounter this particular record is associated with.  In the case of a "new" diagnosis reflecting ongoing/revised information about the condition, this might be distinct from the first encounter in which the underlying condition was first "known".</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -835,10 +836,10 @@
     <t>When in resolution/remission. この状態はいつ治癒／寛解／軽快したか</t>
   </si>
   <si>
-    <t>The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
-  </si>
-  <si>
-    <t>There is no explicit distinction between resolution and remission because in many cases the distinction is not clear. Age is generally used when the patient reports an age at which the Condition abated.  If there is no abatement element, it is unknown whether the condition has resolved or entered remission; applications and users should generally assume that the condition is still valid.  When abatementString exists, it implies the condition is abated.</t>
+    <t>その状態が解消された日付または予想日。これは、「寛解」と呼ばれます。「寛解」または「解決」と関連付けられた多くの意味のオーバーロードのため、「寛解」と呼ばれます。状態は実際には解決されることはありませんが、緩和することができます。 / The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
+  </si>
+  <si>
+    <t>解決」と「寛解」の間に明確な区別はないため、多くの場合、区別が明確ではありません。患者が症状が収まった年齢を報告した場合、年齢が一般的に使用されます。解消要素がない場合、状態が解決したのか、寛解に入ったのかはわかりません。アプリケーションやユーザーは、一般的に条件が有効であると仮定する必要があります。解消文字列が存在する場合、条件が収束したことを意味します。 / There is no explicit distinction between resolution and remission because in many cases the distinction is not clear. Age is generally used when the patient reports an age at which the Condition abated.  If there is no abatement element, it is unknown whether the condition has resolved or entered remission; applications and users should generally assume that the condition is still valid.  When abatementString exists, it implies the condition is abated.</t>
   </si>
   <si>
     <t xml:space="preserve">con-4
@@ -931,8 +932,8 @@
 病状の臨床病期またはグレード。正式な重症度評価を含む場合がある。</t>
   </si>
   <si>
-    <t>con-1:Stage SHALL have summary or assessment {summary.exists() or assessment.exists()}
-ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}</t>
+    <t>con-1:ステージには要約または評価が必要です。 / Stage SHALL have summary or assessment {summary.exists() or assessment.exists()}
+ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}</t>
   </si>
   <si>
     <t>./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="stage/grade"]</t>
@@ -945,10 +946,10 @@
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>エレメント相互参照のためのユニークID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -960,7 +961,7 @@
     <t>Condition.stage.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -973,10 +974,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -986,13 +988,13 @@
     <t>Condition.stage.summary</t>
   </si>
   <si>
-    <t>Simple summary (disease specific)</t>
-  </si>
-  <si>
-    <t>A simple summary of the stage such as "Stage 3". The determination of the stage is disease-specific.</t>
-  </si>
-  <si>
-    <t>Codes describing condition stages (e.g. Cancer stages).</t>
+    <t>簡単な要約（病気特有のもの） / Simple summary (disease specific)</t>
+  </si>
+  <si>
+    <t>ステージ3」といった、単純なステージの概要。ステージの決定は病気によって異なります。 / A simple summary of the stage such as "Stage 3". The determination of the stage is disease-specific.</t>
+  </si>
+  <si>
+    <t>状態段階を説明するコード（例：がんの段階） / Codes describing condition stages (e.g. Cancer stages).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-stage|4.3.0</t>
@@ -1012,10 +1014,10 @@
 </t>
   </si>
   <si>
-    <t>Formal record of assessment</t>
-  </si>
-  <si>
-    <t>Reference to a formal record of the evidence on which the staging assessment is based.</t>
+    <t>評価の公式記録 / Formal record of assessment</t>
+  </si>
+  <si>
+    <t>ステージング評価の根拠となる正式な証拠記録への参照。 / Reference to a formal record of the evidence on which the staging assessment is based.</t>
   </si>
   <si>
     <t>.self</t>
@@ -1024,13 +1026,13 @@
     <t>Condition.stage.type</t>
   </si>
   <si>
-    <t>Kind of staging</t>
-  </si>
-  <si>
-    <t>The kind of staging, such as pathological or clinical staging.</t>
-  </si>
-  <si>
-    <t>Codes describing the kind of condition staging (e.g. clinical or pathological).</t>
+    <t>ステージングの種類 / Kind of staging</t>
+  </si>
+  <si>
+    <t>病理的ステージングや臨床ステージングといった種類のステージング / The kind of staging, such as pathological or clinical staging.</t>
+  </si>
+  <si>
+    <t>状態分類を表すコード（例：臨床的または病理学的）。 / Codes describing the kind of condition staging (e.g. clinical or pathological).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-stage-type|4.3.0</t>
@@ -1049,11 +1051,11 @@
 患者状態を確認または否定した証拠など、状態の検証ステータスの裏付けとなる症状や兆候。</t>
   </si>
   <si>
-    <t>The evidence may be a simple list of coded symptoms/manifestations, or references to observations or formal assessments, or both.</t>
-  </si>
-  <si>
-    <t>con-2:evidence SHALL have code or details {code.exists() or detail.exists()}
-ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}</t>
+    <t>証拠は、コード化された症状/症状の簡単なリスト、または観察や正式な評価への言及、またはその両方である可能性があります。 / The evidence may be a simple list of coded symptoms/manifestations, or references to observations or formal assessments, or both.</t>
+  </si>
+  <si>
+    <t>con-2:証拠にはコードまたは詳細が必要です。 / evidence SHALL have code or details {code.exists() or detail.exists()}
+ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=SPRT].target[classCode=OBS, moodCode=EVN]</t>
@@ -1071,13 +1073,13 @@
     <t>Condition.evidence.code</t>
   </si>
   <si>
-    <t>Manifestation/symptom</t>
-  </si>
-  <si>
-    <t>A manifestation or symptom that led to the recording of this condition.</t>
-  </si>
-  <si>
-    <t>Codes that describe the manifestation or symptoms of a condition.</t>
+    <t>判断した根拠となる兆候や症状 / Manifestation/symptom</t>
+  </si>
+  <si>
+    <t>この状態の記録に至った兆候や症状。 / A manifestation or symptom that led to the recording of this condition.</t>
+  </si>
+  <si>
+    <t>症状や現れ方を記述するコード。 / Codes that describe the manifestation or symptoms of a condition.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom|4.3.0</t>
@@ -1103,10 +1105,10 @@
 </t>
   </si>
   <si>
-    <t>Supporting information found elsewhere</t>
-  </si>
-  <si>
-    <t>Links to other relevant information, including pathology reports.</t>
+    <t>別の場所で見つかったサポート情報 / Supporting information found elsewhere</t>
+  </si>
+  <si>
+    <t>その他関連情報、病理検査報告書などのリンク。 / Links to other relevant information, including pathology reports.</t>
   </si>
   <si>
     <t>Condition.note</t>
@@ -1460,7 +1462,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="73.078125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="100.0703125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="53.95703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
